--- a/data/parameters_table.xlsx
+++ b/data/parameters_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LEHOUX\Maquereau\iml-mackerel\00.0_model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E6DD51-81B2-43DB-9B15-E871F83B392A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661D5AD0-4A83-4C74-8C2C-E56F101D365E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="12672" windowWidth="23256" windowHeight="12456" xr2:uid="{EA117C73-AB9E-4F41-8976-B02C127DD355}"/>
+    <workbookView xWindow="120" yWindow="3612" windowWidth="8016" windowHeight="8880" xr2:uid="{EA117C73-AB9E-4F41-8976-B02C127DD355}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -98,9 +98,6 @@
     <t>Survey measurement error variance</t>
   </si>
   <si>
-    <t xml:space="preserve">Parameter </t>
-  </si>
-  <si>
     <t xml:space="preserve"> Definition </t>
   </si>
   <si>
@@ -108,6 +105,9 @@
   </si>
   <si>
     <t>$$ \sigma^2_{s} $$</t>
+  </si>
+  <si>
+    <t>Parameter</t>
   </si>
 </sst>
 </file>
@@ -163,9 +163,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -203,7 +203,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -309,7 +309,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -451,7 +451,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -460,24 +460,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B03196E-CD7F-469B-A2B6-00C241EB45BA}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.53515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -488,7 +488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -499,7 +499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -510,7 +510,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -521,7 +521,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -532,7 +532,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -554,7 +554,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -565,7 +565,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -576,9 +576,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
@@ -589,5 +589,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Calibri"&amp;12&amp;K000000 Unclassified - Non-Classifié&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>